--- a/docs/Matriz_Infraestructura.xlsx
+++ b/docs/Matriz_Infraestructura.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TrazaDoc — MVP de verificación de integridad y trazabilidad documental en contratos laborales con blockchain permisionada (Hyperledger Fabric)</t>
+          <t>TrazaDoc: MVP de verificación de integridad y trazabilidad documental en contratos laborales con blockchain permisionada (Hyperledger Fabric)</t>
         </is>
       </c>
     </row>
@@ -509,7 +509,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Objetivo específico: OE2 — Diseñar la arquitectura del sistema (UX/UI, software e infraestructura sobre Hyperledger Fabric desplegada en Docker).</t>
+          <t>Objetivo específico: OE2, Diseñar la arquitectura del sistema (UX/UI, software e infraestructura sobre Hyperledger Fabric desplegada en Docker).</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Autoras: Laura Sofia Diaz Suarez · Sofia Ortiz Daza — Universidad Católica de Colombia</t>
+          <t>Autoras: Laura Sofia Diaz Suarez · Sofia Ortiz Daza, Universidad Católica de Colombia</t>
         </is>
       </c>
     </row>
@@ -554,56 +554,56 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>1. Componentes — cada nodo/servicio: tecnología, versión, función, puertos, persistencia, seguridad, dependencias y requisitos que cumple.</t>
+          <t>1. Componentes: cada nodo/servicio: tecnología, versión, función, puertos, persistencia, seguridad, dependencias y requisitos que cumple.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>2. Red Fabric — topología blockchain: organizaciones, canal, consenso, políticas, chaincode.</t>
+          <t>2. Red Fabric: topología blockchain: organizaciones, canal, consenso, políticas, chaincode.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>3. Puertos — mapa de puertos expuestos en el host.</t>
+          <t>3. Puertos: mapa de puertos expuestos en el host.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>4. Configuración — variables de entorno y secretos.</t>
+          <t>4. Configuración: variables de entorno y secretos.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>5. Despliegue — procedimiento reproducible paso a paso.</t>
+          <t>5. Despliegue: procedimiento reproducible paso a paso.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>6. Trazabilidad RNF — qué componente cumple cada requisito no funcional de infraestructura.</t>
+          <t>6. Trazabilidad RNF: qué componente cumple cada requisito no funcional de infraestructura.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>7. Observaciones — decisiones de diseño y diferencias entre lo documentado y lo implementado.</t>
+          <t>7. Observaciones: decisiones de diseño y diferencias entre lo documentado y lo implementado.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>8. Aprobación — registro de revisión del tutor (KPI OE2).</t>
+          <t>8. Aprobación: registro de revisión del tutor (KPI OE2).</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="K11" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" s="7" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>— (solo lo invoca el peer)</t>
+          <t>: (solo lo invoca el peer)</t>
         </is>
       </c>
       <c r="I13" s="7" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -1480,17 +1480,17 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J15" s="7" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>— (servicio en la nube)</t>
+          <t>: (servicio en la nube)</t>
         </is>
       </c>
       <c r="H16" s="6" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Plan de Sprint 0 (D2) y Sprint 2 (D7): OR('Org1MSP.peer','Org2MSP.peer') — basta una organización.</t>
+          <t>Plan de Sprint 0 (D2) y Sprint 2 (D7): OR('Org1MSP.peer','Org2MSP.peer'), basta una organización.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">

--- a/docs/Matriz_Infraestructura.xlsx
+++ b/docs/Matriz_Infraestructura.xlsx
@@ -618,7 +618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>SPA de los 3 roles (Empleado, Verificador, Administrador). Solo conoce la URL del backend (VITE_API_URL).</t>
+          <t>SPA de los 3 roles (Empleado, Verificador, Administrador). Su nginx reenvía /api/* al backend (mismo origen).</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>No conoce ni contacta Fabric ni MongoDB. Publicado solo en localhost.</t>
+          <t>No conoce ni contacta Fabric ni MongoDB. Publicado solo en localhost. nginx: límite de intentos de login por IP, cabeceras CSP/HSTS/nosniff, bloquea /api/fabric.</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -1578,6 +1578,73 @@
       <c r="M16" s="6" t="inlineStr">
         <is>
           <t>Variables SMTP_* en docker/.env</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="7" t="inlineStr">
+        <is>
+          <t>INF-14</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Presentación / borde</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>Proxy HTTPS (solo servidor público)</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>Caddy (caddy:2.10.2-alpine)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>2.10.2</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Termina TLS con certificado Let's Encrypt automático para PUBLIC_DOMAIN y reenvía todo al frontend. Redirige HTTP a HTTPS.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>caddy</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>80, 443 (0.0.0.0)</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Volumen caddy_data (certificado)</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Único servicio expuesto a internet; el NSG de Azure solo abre 80, 443 y 22.</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>INF-01</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr">
+        <is>
+          <t>RNF-05, RNF-21</t>
+        </is>
+      </c>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>docker/up.sh si PUBLIC_DOMAIN tiene valor</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1974,7 +2041,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>0.0.0.0 (todas las interfaces)</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1999,7 +2066,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -2024,7 +2091,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -2049,7 +2116,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -2074,7 +2141,7 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
@@ -2099,7 +2166,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -2124,7 +2191,7 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
@@ -2149,7 +2216,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -2174,7 +2241,7 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
@@ -2199,7 +2266,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>0.0.0.0</t>
+          <t>127.0.0.1 (solo local)</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -2226,35 +2293,62 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
+          <t>127.0.0.1 (solo local)</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>Servicio de operaciones de cada CA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>80 / 443</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>caddy (solo servidor público)</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>HTTP / HTTPS</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
           <t>0.0.0.0</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>Servicio de operaciones de cada CA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="n">
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Entrada pública: certificado y aplicación por HTTPS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="n">
         <v>587</v>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Brevo (externo)</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>SMTP + STARTTLS</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Saliente</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>Envío del correo con el código OTP.</t>
         </is>
@@ -2271,7 +2365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2473,7 +2567,7 @@
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>Puerto publicado del frontend; también define el origen permitido por CORS.</t>
+          <t>Puerto publicado del frontend.</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2584,7 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>http://localhost:8080</t>
+          <t>/api</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -2500,14 +2594,14 @@
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>URL del backend que se compila dentro del frontend (cambiarla exige reconstruir la imagen).</t>
+          <t>Ruta del backend que se compila dentro del frontend; el nginx del frontend la reenvía (cambiarla exige reconstruir la imagen).</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>SMTP_HOST / SMTP_PORT</t>
+          <t>PUBLIC_DOMAIN</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
@@ -2517,7 +2611,7 @@
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>vacío / 587</t>
+          <t>vacío</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -2527,14 +2621,14 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>Servidor de correo (smtp-relay.sendinblue.com). Vacío = el OTP se imprime en los logs del backend (modo desarrollo).</t>
+          <t>Dominio público (Azure). Con valor, up.sh exige secretos propios y enciende Caddy.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>SMTP_USER / SMTP_PASSWORD</t>
+          <t>FRONTEND_ORIGIN</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -2544,24 +2638,24 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>vacío</t>
+          <t>http://localhost:5173</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Login y clave SMTP de Brevo (una clave por persona).</t>
+          <t>Origen permitido por CORS; solo importa con npm run dev.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>SMTP_FROM</t>
+          <t>SMTP_HOST / SMTP_PORT</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
@@ -2571,7 +2665,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>no-reply@contratos.local</t>
+          <t>vacío / 587</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -2581,19 +2675,19 @@
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>Remitente verificado en Brevo (contratosblockchain@gmail.com).</t>
+          <t>Servidor de correo (smtp-relay.sendinblue.com). Vacío = el OTP se imprime en los logs del backend (modo desarrollo).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>SEED_EMAIL</t>
+          <t>SMTP_USER / SMTP_PASSWORD</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>backend/.env</t>
+          <t>docker/.env</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -2603,29 +2697,29 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Buzón real para los usuarios de prueba del seed (buzon+rol@dominio).</t>
+          <t>Login y clave SMTP de Brevo (una clave por persona).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>OTP_TTL_MINUTES / OTP_MAX_ATTEMPTS</t>
+          <t>SMTP_FROM</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>valores por defecto del backend</t>
+          <t>docker/.env</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>5 / 5</t>
+          <t>no-reply@contratos.local</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -2635,24 +2729,24 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>Vigencia e intentos del código OTP.</t>
+          <t>Remitente verificado en Brevo (contratosblockchain@gmail.com).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>SESSION_INACTIVITY_MINUTES</t>
+          <t>SEED_EMAIL</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>valores por defecto del backend</t>
+          <t>backend/.env</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>vacío</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -2662,14 +2756,14 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Cierre de sesión por inactividad (RNF-07).</t>
+          <t>Buzón real para los usuarios de prueba del seed (buzon+rol@dominio).</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>MAX_LOGIN_ATTEMPTS / LOGIN_LOCKOUT_MINUTES</t>
+          <t>OTP_TTL_MINUTES / OTP_MAX_ATTEMPTS</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
@@ -2679,7 +2773,7 @@
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>5 / 15</t>
+          <t>5 / 5</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -2689,32 +2783,86 @@
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>Bloqueo temporal tras intentos fallidos (RF-054).</t>
+          <t>Vigencia e intentos del código OTP.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
+          <t>SESSION_INACTIVITY_MINUTES</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>valores por defecto del backend</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Cierre de sesión por inactividad (RNF-07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>MAX_LOGIN_ATTEMPTS / LOGIN_LOCKOUT_MINUTES</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>valores por defecto del backend</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>5 / 15</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>Bloqueo temporal tras intentos fallidos (RF-054).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
           <t>FABRIC_PEER_ENDPOINT / FABRIC_CRYPTO_PATH</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>valores por defecto del backend</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>peer0.org1.example.com:7051 / /crypto/...</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>Conexión del Gateway al peer y ruta de la identidad montada.</t>
         </is>
@@ -3434,12 +3582,12 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Los puertos de la red Fabric se publican en 0.0.0.0 (todas las interfaces); los de la aplicación solo en 127.0.0.1.</t>
+          <t>Resuelto: network-up.sh publica los puertos de Fabric solo en 127.0.0.1, igual que los de la aplicación.</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Aceptable en local. Para Azure, restringir con reglas de red (NSG) o publicar solo en localhost.</t>
+          <t>En Azure solo Caddy escucha fuera (80/443); además el NSG solo abre 80, 443 y 22.</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3609,12 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Solo Docker local.</t>
+          <t>Docker local; despliegue en Azure preparado (Caddy + HTTPS, guía DESPLIEGUE-AZURE.md).</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Pendiente: despliegue en Azure (criterio 4 de la Definición de Terminado). Las mediciones de rendimiento S11/S13 son en Docker local.</t>
+          <t>Pendiente ejecutarlo en la VM (criterio 4 de la Definición de Terminado). Las mediciones de rendimiento S11/S13 son en Docker local.</t>
         </is>
       </c>
     </row>
